--- a/information_forms/022_former_employee_information_form--information_forms.xlsx
+++ b/information_forms/022_former_employee_information_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'poor_compensation',_'label':_'poor_compensation'}</t>
+          <t>poor_compensation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'poor_compensation', 'label': 'poor_compensation'}</t>
+          <t>poor compensation</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'lack_of_challenge',_'label':_'lack_of_challenge'}</t>
+          <t>lack_of_challenge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'lack_of_challenge', 'label': 'lack_of_challenge'}</t>
+          <t>lack of challenge</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'poor_management',_'label':_'poor_management'}</t>
+          <t>poor_management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'poor_management', 'label': 'poor_management'}</t>
+          <t>poor management</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'lack_of_growth_opportunities',_'label':_'lack_of_growth_opportunities'}</t>
+          <t>lack_of_growth_opportunities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'lack_of_growth_opportunities', 'label': 'lack_of_growth_opportunities'}</t>
+          <t>lack of growth opportunities</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'lack_of_challenge',_'label':_'lack_of_challenge'}</t>
+          <t>lack_of_challenge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'lack_of_challenge', 'label': 'lack_of_challenge'}</t>
+          <t>lack of challenge</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'no_match_with_team',_'label':_'no_match_with_team'}</t>
+          <t>no_match_with_team</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'no_match_with_team', 'label': 'no_match_with_team'}</t>
+          <t>no match with team</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'no_clear_goals',_'label':_'no_clear_goals'}</t>
+          <t>no_clear_goals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'no_clear_goals', 'label': 'no_clear_goals'}</t>
+          <t>no clear goals</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'poor_communication',_'label':_'poor_communication'}</t>
+          <t>poor_communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'poor_communication', 'label': 'poor_communication'}</t>
+          <t>poor communication</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'conflicting_priorities',_'label':_'conflicting_priorities'}</t>
+          <t>conflicting_priorities</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'conflicting_priorities', 'label': 'conflicting_priorities'}</t>
+          <t>conflicting priorities</t>
         </is>
       </c>
     </row>
